--- a/Supplementary Information/S3 PBMC Samples.xlsx
+++ b/Supplementary Information/S3 PBMC Samples.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\rrms\bulk\final_assignment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\rrms\Supplementary Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FBE34D-5AB7-4A4D-8DA8-D85911AC4DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C9684D-E08C-41BB-9E19-D152052186C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5558" yWindow="2730" windowWidth="21600" windowHeight="11333" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="705" yWindow="705" windowWidth="26183" windowHeight="14408" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PBMC Samples" sheetId="1" r:id="rId1"/>
@@ -1313,7 +1313,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1330,6 +1330,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1379,7 +1385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1390,6 +1396,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1693,23 +1700,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K241"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="14" width="15.46484375" customWidth="1"/>
+    <col min="1" max="1" width="12" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22" style="4" customWidth="1"/>
+    <col min="5" max="5" width="6" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28" style="4" customWidth="1"/>
+    <col min="8" max="8" width="25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="30" style="4" customWidth="1"/>
+    <col min="10" max="10" width="20" style="4" customWidth="1"/>
+    <col min="11" max="11" width="13" style="4" customWidth="1"/>
+    <col min="12" max="14" width="15.46484375" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="8.796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1744,7 +1752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1779,7 +1787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1814,7 +1822,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -1849,7 +1857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -1884,7 +1892,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1919,7 +1927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
@@ -1954,7 +1962,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -1989,7 +1997,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
@@ -2024,7 +2032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -2059,7 +2067,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
@@ -2094,7 +2102,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>42</v>
       </c>
@@ -2129,7 +2137,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
@@ -2164,7 +2172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
@@ -2199,7 +2207,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>50</v>
       </c>
@@ -2234,7 +2242,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>52</v>
       </c>
@@ -2269,7 +2277,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
@@ -2304,7 +2312,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
@@ -2339,7 +2347,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>56</v>
       </c>
@@ -2374,7 +2382,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -2409,7 +2417,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
@@ -2444,7 +2452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
@@ -2479,7 +2487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>63</v>
       </c>
@@ -2514,7 +2522,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>66</v>
       </c>
@@ -2549,7 +2557,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>67</v>
       </c>
@@ -2584,7 +2592,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>69</v>
       </c>
@@ -2619,7 +2627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>70</v>
       </c>
@@ -2654,7 +2662,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>73</v>
       </c>
@@ -2689,7 +2697,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>74</v>
       </c>
@@ -2724,7 +2732,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>76</v>
       </c>
@@ -2759,7 +2767,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>77</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>79</v>
       </c>
@@ -2829,7 +2837,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>80</v>
       </c>
@@ -2864,7 +2872,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>82</v>
       </c>
@@ -2899,7 +2907,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>83</v>
       </c>
@@ -2934,7 +2942,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>85</v>
       </c>
@@ -2969,7 +2977,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>86</v>
       </c>
@@ -3004,7 +3012,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>88</v>
       </c>
@@ -3039,7 +3047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>89</v>
       </c>
@@ -3074,7 +3082,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>91</v>
       </c>
@@ -3109,7 +3117,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>92</v>
       </c>
@@ -3144,7 +3152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>94</v>
       </c>
@@ -3179,7 +3187,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>96</v>
       </c>
@@ -3214,7 +3222,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>98</v>
       </c>
@@ -3249,7 +3257,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>99</v>
       </c>
@@ -3284,7 +3292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>101</v>
       </c>
@@ -3319,7 +3327,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>102</v>
       </c>
@@ -3354,7 +3362,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>105</v>
       </c>
@@ -3389,7 +3397,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>106</v>
       </c>
@@ -3424,7 +3432,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>108</v>
       </c>
@@ -3459,7 +3467,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>109</v>
       </c>
@@ -3494,7 +3502,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>111</v>
       </c>
@@ -3529,7 +3537,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>112</v>
       </c>
@@ -3564,7 +3572,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>114</v>
       </c>
@@ -3599,7 +3607,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>115</v>
       </c>
@@ -3634,7 +3642,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>118</v>
       </c>
@@ -3669,7 +3677,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>119</v>
       </c>
@@ -3704,7 +3712,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>121</v>
       </c>
@@ -3739,7 +3747,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>124</v>
       </c>
@@ -3774,7 +3782,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>125</v>
       </c>
@@ -3809,7 +3817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>126</v>
       </c>
@@ -3844,7 +3852,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>128</v>
       </c>
@@ -3879,7 +3887,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>130</v>
       </c>
@@ -3914,7 +3922,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>131</v>
       </c>
@@ -3949,7 +3957,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>134</v>
       </c>
@@ -3984,7 +3992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>136</v>
       </c>
@@ -4019,7 +4027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>137</v>
       </c>
@@ -4054,7 +4062,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>140</v>
       </c>
@@ -4089,7 +4097,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>141</v>
       </c>
@@ -4124,7 +4132,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>143</v>
       </c>
@@ -4159,7 +4167,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>144</v>
       </c>
@@ -4194,7 +4202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>148</v>
       </c>
@@ -4229,7 +4237,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>149</v>
       </c>
@@ -4264,7 +4272,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>151</v>
       </c>
@@ -4299,7 +4307,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>152</v>
       </c>
@@ -4334,7 +4342,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>154</v>
       </c>
@@ -4369,7 +4377,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>156</v>
       </c>
@@ -4404,7 +4412,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>157</v>
       </c>
@@ -4439,7 +4447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>160</v>
       </c>
@@ -4474,7 +4482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>161</v>
       </c>
@@ -4509,7 +4517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>163</v>
       </c>
@@ -4544,7 +4552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>164</v>
       </c>
@@ -4579,7 +4587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>166</v>
       </c>
@@ -4614,7 +4622,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>167</v>
       </c>
@@ -4649,7 +4657,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>169</v>
       </c>
@@ -4684,7 +4692,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>172</v>
       </c>
@@ -4719,7 +4727,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>173</v>
       </c>
@@ -4754,7 +4762,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>175</v>
       </c>
@@ -4789,7 +4797,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>177</v>
       </c>
@@ -4824,7 +4832,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>178</v>
       </c>
@@ -4859,7 +4867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>180</v>
       </c>
@@ -4894,7 +4902,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>181</v>
       </c>
@@ -4929,7 +4937,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>183</v>
       </c>
@@ -4964,7 +4972,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>185</v>
       </c>
@@ -4999,7 +5007,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>186</v>
       </c>
@@ -5034,7 +5042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>188</v>
       </c>
@@ -5069,7 +5077,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>189</v>
       </c>
@@ -5104,7 +5112,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>191</v>
       </c>
@@ -5139,7 +5147,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>192</v>
       </c>
@@ -5174,7 +5182,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>194</v>
       </c>
@@ -5209,7 +5217,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>195</v>
       </c>
@@ -5244,7 +5252,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>197</v>
       </c>
@@ -5279,7 +5287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>198</v>
       </c>
@@ -5314,7 +5322,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>200</v>
       </c>
@@ -5349,7 +5357,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>201</v>
       </c>
@@ -5384,7 +5392,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>203</v>
       </c>
@@ -5419,7 +5427,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>205</v>
       </c>
@@ -5454,7 +5462,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>206</v>
       </c>
@@ -5489,7 +5497,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>208</v>
       </c>
@@ -5524,7 +5532,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>209</v>
       </c>
@@ -5559,7 +5567,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>211</v>
       </c>
@@ -5594,7 +5602,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>212</v>
       </c>
@@ -5629,7 +5637,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>214</v>
       </c>
@@ -5664,7 +5672,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>215</v>
       </c>
@@ -5699,7 +5707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>217</v>
       </c>
@@ -5734,7 +5742,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>218</v>
       </c>
@@ -5769,7 +5777,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>220</v>
       </c>
@@ -5804,7 +5812,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>221</v>
       </c>
@@ -5839,7 +5847,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>223</v>
       </c>
@@ -5874,7 +5882,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>224</v>
       </c>
@@ -5909,7 +5917,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>226</v>
       </c>
@@ -5944,7 +5952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>227</v>
       </c>
@@ -5979,7 +5987,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>228</v>
       </c>
@@ -6014,7 +6022,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>229</v>
       </c>
@@ -6049,7 +6057,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>230</v>
       </c>
@@ -6084,7 +6092,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>231</v>
       </c>
@@ -6119,7 +6127,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>234</v>
       </c>
@@ -6154,7 +6162,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>235</v>
       </c>
@@ -6189,7 +6197,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>237</v>
       </c>
@@ -6224,7 +6232,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>238</v>
       </c>
@@ -6259,7 +6267,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>240</v>
       </c>
@@ -6294,7 +6302,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>241</v>
       </c>
@@ -6329,7 +6337,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>243</v>
       </c>
@@ -6364,7 +6372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>244</v>
       </c>
@@ -6399,7 +6407,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>246</v>
       </c>
@@ -6434,7 +6442,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>247</v>
       </c>
@@ -6469,7 +6477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>249</v>
       </c>
@@ -6504,7 +6512,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>250</v>
       </c>
@@ -6539,7 +6547,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>252</v>
       </c>
@@ -6574,7 +6582,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>254</v>
       </c>
@@ -6609,7 +6617,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>256</v>
       </c>
@@ -6644,7 +6652,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>257</v>
       </c>
@@ -6679,7 +6687,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>259</v>
       </c>
@@ -6714,7 +6722,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>260</v>
       </c>
@@ -6749,7 +6757,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>261</v>
       </c>
@@ -6784,7 +6792,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>263</v>
       </c>
@@ -6819,7 +6827,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>264</v>
       </c>
@@ -6854,7 +6862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>266</v>
       </c>
@@ -6889,7 +6897,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>267</v>
       </c>
@@ -6924,7 +6932,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>269</v>
       </c>
@@ -6959,7 +6967,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>270</v>
       </c>
@@ -6994,7 +7002,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>272</v>
       </c>
@@ -7029,7 +7037,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>273</v>
       </c>
@@ -7064,7 +7072,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>275</v>
       </c>
@@ -7099,7 +7107,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>276</v>
       </c>
@@ -7134,7 +7142,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>278</v>
       </c>
@@ -7169,7 +7177,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>280</v>
       </c>
@@ -7204,7 +7212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>281</v>
       </c>
@@ -7239,7 +7247,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>283</v>
       </c>
@@ -7274,7 +7282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>284</v>
       </c>
@@ -7309,7 +7317,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>286</v>
       </c>
@@ -7344,7 +7352,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>287</v>
       </c>
@@ -7379,7 +7387,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>289</v>
       </c>
@@ -7414,7 +7422,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>290</v>
       </c>
@@ -7449,7 +7457,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>292</v>
       </c>
@@ -7484,7 +7492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>294</v>
       </c>
@@ -7519,7 +7527,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>295</v>
       </c>
@@ -7554,7 +7562,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>297</v>
       </c>
@@ -7589,7 +7597,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
         <v>298</v>
       </c>
@@ -7624,7 +7632,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>299</v>
       </c>
@@ -7659,7 +7667,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>301</v>
       </c>
@@ -7694,7 +7702,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>302</v>
       </c>
@@ -7729,7 +7737,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>305</v>
       </c>
@@ -7764,7 +7772,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>307</v>
       </c>
@@ -7799,7 +7807,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>308</v>
       </c>
@@ -7834,7 +7842,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>310</v>
       </c>
@@ -7869,7 +7877,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>311</v>
       </c>
@@ -7904,7 +7912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>313</v>
       </c>
@@ -7939,7 +7947,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>314</v>
       </c>
@@ -7974,7 +7982,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>316</v>
       </c>
@@ -8009,7 +8017,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>317</v>
       </c>
@@ -8044,7 +8052,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>319</v>
       </c>
@@ -8079,7 +8087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>320</v>
       </c>
@@ -8114,7 +8122,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>322</v>
       </c>
@@ -8149,7 +8157,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>323</v>
       </c>
@@ -8184,7 +8192,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>325</v>
       </c>
@@ -8219,7 +8227,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>326</v>
       </c>
@@ -8254,7 +8262,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>328</v>
       </c>
@@ -8289,7 +8297,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>329</v>
       </c>
@@ -8324,7 +8332,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>331</v>
       </c>
@@ -8359,7 +8367,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>332</v>
       </c>
@@ -8394,7 +8402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>334</v>
       </c>
@@ -8429,7 +8437,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>336</v>
       </c>
@@ -8464,7 +8472,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>337</v>
       </c>
@@ -8499,7 +8507,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>339</v>
       </c>
@@ -8534,7 +8542,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>340</v>
       </c>
@@ -8569,7 +8577,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>342</v>
       </c>
@@ -8604,7 +8612,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>343</v>
       </c>
@@ -8639,7 +8647,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>346</v>
       </c>
@@ -8674,7 +8682,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>347</v>
       </c>
@@ -8709,7 +8717,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
         <v>349</v>
       </c>
@@ -8744,7 +8752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>351</v>
       </c>
@@ -8779,7 +8787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
         <v>352</v>
       </c>
@@ -8814,7 +8822,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>354</v>
       </c>
@@ -8849,7 +8857,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
         <v>355</v>
       </c>
@@ -8884,7 +8892,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>357</v>
       </c>
@@ -8919,7 +8927,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
         <v>359</v>
       </c>
@@ -8954,7 +8962,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>360</v>
       </c>
@@ -8989,7 +8997,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
         <v>362</v>
       </c>
@@ -9024,7 +9032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>363</v>
       </c>
@@ -9059,7 +9067,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
         <v>365</v>
       </c>
@@ -9094,7 +9102,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>366</v>
       </c>
@@ -9129,7 +9137,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
         <v>368</v>
       </c>
@@ -9164,7 +9172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>369</v>
       </c>
@@ -9199,7 +9207,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
         <v>371</v>
       </c>
@@ -9234,7 +9242,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>373</v>
       </c>
@@ -9269,7 +9277,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
         <v>374</v>
       </c>
@@ -9304,7 +9312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>376</v>
       </c>
@@ -9339,7 +9347,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
         <v>379</v>
       </c>
@@ -9374,7 +9382,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>381</v>
       </c>
@@ -9409,7 +9417,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
         <v>382</v>
       </c>
@@ -9442,7 +9450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>385</v>
       </c>
@@ -9475,7 +9483,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
         <v>388</v>
       </c>
@@ -9508,7 +9516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>390</v>
       </c>
@@ -9541,7 +9549,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
         <v>392</v>
       </c>
@@ -9574,7 +9582,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>394</v>
       </c>
@@ -9607,7 +9615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
         <v>396</v>
       </c>
@@ -9640,7 +9648,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>398</v>
       </c>
@@ -9673,7 +9681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
         <v>401</v>
       </c>
@@ -9706,7 +9714,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>403</v>
       </c>
@@ -9739,7 +9747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
         <v>405</v>
       </c>
@@ -9772,7 +9780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>407</v>
       </c>
@@ -9805,7 +9813,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
         <v>409</v>
       </c>
@@ -9838,7 +9846,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>411</v>
       </c>
@@ -9871,7 +9879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" s="3" t="s">
         <v>413</v>
       </c>
@@ -9904,7 +9912,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>415</v>
       </c>
@@ -9937,7 +9945,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
         <v>417</v>
       </c>
@@ -9970,7 +9978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>419</v>
       </c>
@@ -10003,7 +10011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
         <v>421</v>
       </c>
@@ -10036,7 +10044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>423</v>
       </c>
@@ -10069,7 +10077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
         <v>425</v>
       </c>
